--- a/data.mn/public/datasets/health-facilities-national.xlsx
+++ b/data.mn/public/datasets/health-facilities-national.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,16 +416,130 @@
   </sheetPr>
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>facilities_count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3244</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4343</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4459</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4187</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4652</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4746</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4914</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>байгууллагын_тоо</t>
         </is>
       </c>
     </row>
